--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4382,61 +4382,61 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="12" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:9">
+      <c r="A27" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="C27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="9">
         <v>6600</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="8">
         <v>29</v>
       </c>
-      <c r="F27" s="14">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="12" t="s">
+      <c r="F27" s="10">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="12" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:9">
+      <c r="A28" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="9">
         <v>6600</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="8">
         <v>29</v>
       </c>
-      <c r="F28" s="14">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="12" t="s">
+      <c r="F28" s="10">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>96</v>
       </c>
     </row>
@@ -15162,9 +15162,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G417" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="🟡 第2波"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="🟡 第2波"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4440,59 +4440,59 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="12" t="s">
+    <row r="29" s="1" customFormat="1" spans="1:9">
+      <c r="A29" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="13">
+      <c r="C29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="9">
         <v>6600</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="8">
         <v>30</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="10">
         <v>0.49</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="12"/>
-      <c r="I29" t="s">
+      <c r="G29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="12" t="s">
+    <row r="30" s="1" customFormat="1" spans="1:9">
+      <c r="A30" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="13">
+      <c r="C30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="9">
         <v>6600</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="8">
         <v>30</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="10">
         <v>0.73</v>
       </c>
-      <c r="G30" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="12" t="s">
+      <c r="G30" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>101</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4697,32 +4697,32 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="12" t="s">
+    <row r="38" s="1" customFormat="1" spans="1:9">
+      <c r="A38" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="C38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="9">
         <v>5400</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="8">
         <v>29</v>
       </c>
-      <c r="F38" s="14">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="12" t="s">
+      <c r="F38" s="10">
+        <v>0</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4869,88 +4869,88 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="12" t="s">
+    <row r="44" s="1" customFormat="1" ht="14" customHeight="1" spans="1:9">
+      <c r="A44" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="13">
+      <c r="C44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="9">
         <v>4400</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="8">
         <v>21</v>
       </c>
-      <c r="F44" s="14">
-        <v>0</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="12" t="s">
+      <c r="F44" s="10">
+        <v>0</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="12" t="s">
+    <row r="45" s="1" customFormat="1" spans="1:9">
+      <c r="A45" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="13">
+      <c r="C45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="9">
         <v>4400</v>
       </c>
-      <c r="E45" s="12">
-        <v>23</v>
-      </c>
-      <c r="F45" s="14">
+      <c r="E45" s="8">
+        <v>23</v>
+      </c>
+      <c r="F45" s="10">
         <v>1.68</v>
       </c>
-      <c r="G45" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="12"/>
-      <c r="I45" t="s">
+      <c r="G45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="8"/>
+      <c r="I45" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="12" t="s">
+    <row r="46" s="1" customFormat="1" spans="1:9">
+      <c r="A46" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="13">
+      <c r="C46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="9">
         <v>4400</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="8">
         <v>25</v>
       </c>
-      <c r="F46" s="14">
+      <c r="F46" s="10">
         <v>0.49</v>
       </c>
-      <c r="G46" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H46" s="12" t="s">
+      <c r="G46" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="1" t="s">
         <v>141</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4954,61 +4954,61 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="12" t="s">
+    <row r="47" s="1" customFormat="1" spans="1:9">
+      <c r="A47" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="C47" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="9">
         <v>4400</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="8">
         <v>26</v>
       </c>
-      <c r="F47" s="14">
-        <v>0</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="12" t="s">
+      <c r="F47" s="10">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="12" t="s">
+    <row r="48" s="1" customFormat="1" spans="1:9">
+      <c r="A48" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="13">
+      <c r="C48" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="9">
         <v>4400</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="8">
         <v>27</v>
       </c>
-      <c r="F48" s="14">
-        <v>0</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="12" t="s">
+      <c r="F48" s="10">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>147</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -5242,61 +5242,61 @@
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="12" t="s">
+    <row r="57" s="1" customFormat="1" spans="1:9">
+      <c r="A57" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="13">
+      <c r="C57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="9">
         <v>3600</v>
       </c>
-      <c r="E57" s="12">
-        <v>23</v>
-      </c>
-      <c r="F57" s="14">
-        <v>0</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" s="12" t="s">
+      <c r="E57" s="8">
+        <v>23</v>
+      </c>
+      <c r="F57" s="10">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="12" t="s">
+    <row r="58" s="1" customFormat="1" spans="1:9">
+      <c r="A58" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" s="13">
+      <c r="C58" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="9">
         <v>3600</v>
       </c>
-      <c r="E58" s="12">
-        <v>23</v>
-      </c>
-      <c r="F58" s="14">
-        <v>0</v>
-      </c>
-      <c r="G58" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H58" s="12" t="s">
+      <c r="E58" s="8">
+        <v>23</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="1" t="s">
         <v>49</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -5300,30 +5300,30 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="12" t="s">
+    <row r="59" s="1" customFormat="1" spans="1:9">
+      <c r="A59" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="13">
+      <c r="C59" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="9">
         <v>3600</v>
       </c>
-      <c r="E59" s="12">
+      <c r="E59" s="8">
         <v>24</v>
       </c>
-      <c r="F59" s="14">
-        <v>0</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="12"/>
-      <c r="I59" t="s">
+      <c r="F59" s="10">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="8"/>
+      <c r="I59" s="1" t="s">
         <v>52</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13340"/>
+    <workbookView windowWidth="30240" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -5327,32 +5327,32 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="12" t="s">
+    <row r="60" s="1" customFormat="1" spans="1:9">
+      <c r="A60" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="9">
         <v>3600</v>
       </c>
-      <c r="E60" s="12">
+      <c r="E60" s="8">
         <v>25</v>
       </c>
-      <c r="F60" s="14">
-        <v>0</v>
-      </c>
-      <c r="G60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="12" t="s">
+      <c r="F60" s="10">
+        <v>0</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="1" t="s">
         <v>96</v>
       </c>
     </row>
